--- a/artfynd/A 57757-2024 artfynd.xlsx
+++ b/artfynd/A 57757-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>114560353</v>
       </c>
       <c r="B2" t="n">
-        <v>57624</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,16 +784,11 @@
         <v>114560222</v>
       </c>
       <c r="B3" t="n">
-        <v>57734</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58439</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -900,16 +890,11 @@
         <v>114560226</v>
       </c>
       <c r="B4" t="n">
-        <v>57734</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58439</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -1005,6 +990,112 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>114560420</v>
+      </c>
+      <c r="B5" t="n">
+        <v>58085</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>205976</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Gråkråka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Corvus corone cornix</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Stadsskogen, Vg</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>352143</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6422222</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Alingsås</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Alingsås</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2023-04-26</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2023-04-26</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Oskar Kullingsjö</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Oskar Kullingsjö</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 57757-2024 artfynd.xlsx
+++ b/artfynd/A 57757-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114560353</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114560222</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -990,6 +1005,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114560226</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1096,8 +1116,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114560420</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>